--- a/5_cobranza/inputs/pagos_efectivo/pagos_efectivo.xlsx
+++ b/5_cobranza/inputs/pagos_efectivo/pagos_efectivo.xlsx
@@ -782,6 +782,9 @@
       <c r="I3" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J3" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -823,6 +826,9 @@
       <c r="I4" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J4" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -864,6 +870,9 @@
       <c r="I5" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J5" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -905,6 +914,9 @@
       <c r="I6" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J6" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -942,6 +954,9 @@
       <c r="I7" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J7" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -983,6 +998,9 @@
       <c r="I8" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J8" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -1024,6 +1042,9 @@
       <c r="I9" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J9" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -1061,6 +1082,9 @@
       <c r="I10" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J10" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -1102,6 +1126,9 @@
       <c r="I11" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J11" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -1139,6 +1166,9 @@
       <c r="I12" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J12" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -1180,6 +1210,9 @@
       <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J13" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -1217,6 +1250,9 @@
       <c r="I14" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J14" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -1258,6 +1294,9 @@
       <c r="I15" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J15" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -1299,6 +1338,9 @@
       <c r="I16" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J16" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1340,6 +1382,9 @@
       <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J17" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -1381,6 +1426,9 @@
       <c r="I18" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J18" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -1422,6 +1470,9 @@
       <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J19" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -1459,6 +1510,9 @@
       <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J20" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -1496,6 +1550,9 @@
       <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J21" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -1533,6 +1590,9 @@
       <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J22" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -1570,6 +1630,9 @@
       <c r="I23" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J23" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -1607,6 +1670,9 @@
       <c r="I24" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J24" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1644,6 +1710,9 @@
       <c r="I25" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J25" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
@@ -1681,6 +1750,9 @@
       <c r="I26" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J26" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
@@ -1718,6 +1790,9 @@
       <c r="I27" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J27" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -1755,6 +1830,9 @@
       <c r="I28" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J28" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -1792,6 +1870,9 @@
       <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J29" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -1829,6 +1910,9 @@
       <c r="I30" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J30" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -1866,6 +1950,9 @@
       <c r="I31" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J31" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
@@ -1903,20 +1990,23 @@
       <c r="I32" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J32" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>46179</v>
@@ -1940,20 +2030,23 @@
       <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J33" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>46179</v>
@@ -1973,20 +2066,27 @@
           <t>Wilder Trujillo</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
@@ -2010,12 +2110,11 @@
           <t>Wilder Trujillo</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H35" s="12" t="inlineStr"/>
       <c r="I35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2027,11 +2126,11 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D36" s="16" t="n">
         <v>46179</v>
@@ -2055,20 +2154,23 @@
       <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J36" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>46179</v>
@@ -2092,20 +2194,23 @@
       <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J37" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="D38" s="16" t="n">
         <v>46179</v>
@@ -2129,6 +2234,9 @@
       <c r="I38" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J38" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
@@ -2138,18 +2246,18 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>mesa_1</t>
+          <t>mesa_2</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -2159,27 +2267,30 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Wilder Trujillo</t>
+          <t>Yerald Romero</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr"/>
       <c r="I39" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J39" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D40" s="16" t="n">
         <v>46178</v>
@@ -2203,20 +2314,23 @@
       <c r="I40" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J40" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>46178</v>
@@ -2240,20 +2354,23 @@
       <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J41" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D42" s="16" t="n">
         <v>46178</v>
@@ -2277,20 +2394,23 @@
       <c r="I42" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J42" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>46178</v>
@@ -2314,20 +2434,23 @@
       <c r="I43" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J43" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="D44" s="16" t="n">
         <v>46178</v>
@@ -2347,24 +2470,31 @@
           <t>Yerald Romero</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr"/>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>46178</v>
@@ -2386,26 +2516,29 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>pago mixto</t>
         </is>
       </c>
       <c r="I45" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D46" s="16" t="n">
         <v>46178</v>
@@ -2434,22 +2567,22 @@
         <v>4</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>46178</v>
@@ -2469,31 +2602,27 @@
           <t>Yerald Romero</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>pago mixto</t>
-        </is>
-      </c>
+      <c r="H47" s="12" t="inlineStr"/>
       <c r="I47" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="D48" s="16" t="n">
         <v>46178</v>
@@ -2517,20 +2646,23 @@
       <c r="I48" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J48" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>46178</v>
@@ -2550,24 +2682,31 @@
           <t>Yerald Romero</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr"/>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>pago fracionado</t>
+        </is>
+      </c>
       <c r="I49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D50" s="16" t="n">
         <v>46178</v>
@@ -2593,6 +2732,9 @@
         </is>
       </c>
       <c r="I50" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2604,11 +2746,11 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D51" s="16" t="n">
         <v>46178</v>
@@ -2634,13 +2776,16 @@
         </is>
       </c>
       <c r="I51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2649,7 +2794,7 @@
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D52" s="16" t="n">
         <v>46178</v>
@@ -2671,26 +2816,29 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>pago fracionado</t>
+          <t>inconprensible</t>
         </is>
       </c>
       <c r="I52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D53" s="16" t="n">
         <v>46178</v>
@@ -2712,26 +2860,29 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>inconprensible</t>
+          <t>pago fracionado</t>
         </is>
       </c>
       <c r="I53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D54" s="16" t="n">
         <v>46178</v>
@@ -2753,26 +2904,29 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>pago fracionado</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="D55" s="16" t="n">
         <v>46178</v>
@@ -2794,26 +2948,29 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>faena adelantada</t>
         </is>
       </c>
       <c r="I55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="D56" s="16" t="n">
         <v>46178</v>
@@ -2835,26 +2992,29 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>faena adelantada</t>
+          <t>pago fracionado</t>
         </is>
       </c>
       <c r="I56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D57" s="16" t="n">
         <v>46178</v>
@@ -2878,20 +3038,23 @@
       <c r="I57" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J57" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D58" s="16" t="n">
         <v>46178</v>
@@ -2917,22 +3080,25 @@
         </is>
       </c>
       <c r="I58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>12A</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="D59" s="16" t="n">
         <v>46178</v>
@@ -2952,24 +3118,31 @@
           <t>Yerald Romero</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr"/>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D60" s="16" t="n">
         <v>46178</v>
@@ -2995,22 +3168,25 @@
         </is>
       </c>
       <c r="I60" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D61" s="16" t="n">
         <v>46178</v>
@@ -3036,22 +3212,25 @@
         </is>
       </c>
       <c r="I61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D62" s="16" t="n">
         <v>46178</v>
@@ -3073,26 +3252,29 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>pago fracionado</t>
+          <t>Exoneracion</t>
         </is>
       </c>
       <c r="I62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D63" s="16" t="n">
         <v>46178</v>
@@ -3114,26 +3296,29 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>Exoneracion</t>
         </is>
       </c>
       <c r="I63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="D64" s="16" t="n">
         <v>46178</v>
@@ -3159,22 +3344,25 @@
         </is>
       </c>
       <c r="I64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>122</v>
+        <v>18.5</v>
       </c>
       <c r="D65" s="16" t="n">
         <v>46178</v>
@@ -3196,26 +3384,29 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Exoneracion</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="D66" s="16" t="n">
         <v>46178</v>
@@ -3237,17 +3428,20 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>Exoneracion</t>
+          <t>pago fracionado</t>
         </is>
       </c>
       <c r="I66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -3256,7 +3450,7 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>18.5</v>
+        <v>44</v>
       </c>
       <c r="D67" s="16" t="n">
         <v>46178</v>
@@ -3276,28 +3470,27 @@
           <t>Yerald Romero</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H67" s="12" t="inlineStr"/>
       <c r="I67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D68" s="16" t="n">
         <v>46178</v>
@@ -3319,33 +3512,36 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>pago fracionado</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D69" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>mesa_2</t>
+          <t>mesa_3</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -3355,34 +3551,41 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Yerald Romero</t>
-        </is>
-      </c>
-      <c r="H69" s="12" t="inlineStr"/>
+          <t>Janet Villanueva</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="D70" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>mesa_2</t>
+          <t>mesa_3</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -3392,31 +3595,30 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>Yerald Romero</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+          <t>Janet Villanueva</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr"/>
       <c r="I70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D71" s="16" t="n">
         <v>46178</v>
@@ -3438,26 +3640,29 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>exoneracion</t>
         </is>
       </c>
       <c r="I71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D72" s="16" t="n">
         <v>46178</v>
@@ -3477,24 +3682,31 @@
           <t>Janet Villanueva</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr"/>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D73" s="16" t="n">
         <v>46178</v>
@@ -3516,26 +3728,29 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>exoneracion</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="D74" s="16" t="n">
         <v>46178</v>
@@ -3557,26 +3772,29 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>pago fraccionado</t>
+          <t>exoneracion</t>
         </is>
       </c>
       <c r="I74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D75" s="16" t="n">
         <v>46178</v>
@@ -3596,28 +3814,27 @@
           <t>Janet Villanueva</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H75" s="12" t="inlineStr"/>
       <c r="I75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D76" s="16" t="n">
         <v>46178</v>
@@ -3637,28 +3854,27 @@
           <t>Janet Villanueva</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
-        <is>
-          <t>exoneracion</t>
-        </is>
-      </c>
+      <c r="H76" s="12" t="inlineStr"/>
       <c r="I76" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D77" s="16" t="n">
         <v>46178</v>
@@ -3678,24 +3894,31 @@
           <t>Janet Villanueva</t>
         </is>
       </c>
-      <c r="H77" s="12" t="inlineStr"/>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C78" s="7" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D78" s="16" t="n">
         <v>46178</v>
@@ -3715,24 +3938,31 @@
           <t>Janet Villanueva</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr"/>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D79" s="16" t="n">
         <v>46178</v>
@@ -3754,26 +3984,29 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>pago fraccionado</t>
         </is>
       </c>
       <c r="I79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C80" s="7" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D80" s="16" t="n">
         <v>46178</v>
@@ -3795,26 +4028,29 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>pago fraccionado</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I80" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="D81" s="16" t="n">
         <v>46178</v>
@@ -3836,26 +4072,29 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>pago fraccionado</t>
+          <t>recuperacion multa</t>
         </is>
       </c>
       <c r="I81" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C82" s="7" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D82" s="16" t="n">
         <v>46178</v>
@@ -3877,22 +4116,25 @@
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>pago fraccionado</t>
         </is>
       </c>
       <c r="I82" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C83" s="7" t="n">
@@ -3918,17 +4160,20 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>recuperacion multa</t>
+          <t>incomprensible</t>
         </is>
       </c>
       <c r="I83" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -3937,7 +4182,7 @@
         </is>
       </c>
       <c r="C84" s="7" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D84" s="16" t="n">
         <v>46178</v>
@@ -3959,26 +4204,29 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>pago fraccionado</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="D85" s="16" t="n">
         <v>46178</v>
@@ -3998,28 +4246,27 @@
           <t>Janet Villanueva</t>
         </is>
       </c>
-      <c r="H85" s="12" t="inlineStr">
-        <is>
-          <t>incomprensible</t>
-        </is>
-      </c>
+      <c r="H85" s="12" t="inlineStr"/>
       <c r="I85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C86" s="7" t="n">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="D86" s="16" t="n">
         <v>46178</v>
@@ -4041,26 +4288,29 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>exoneracion</t>
         </is>
       </c>
       <c r="I86" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="D87" s="16" t="n">
         <v>46178</v>
@@ -4080,8 +4330,15 @@
           <t>Janet Villanueva</t>
         </is>
       </c>
-      <c r="H87" s="12" t="inlineStr"/>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>incomprensible</t>
+        </is>
+      </c>
       <c r="I87" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4093,11 +4350,11 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C88" s="7" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="D88" s="16" t="n">
         <v>46178</v>
@@ -4119,26 +4376,29 @@
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>exoneracion</t>
+          <t>converzar</t>
         </is>
       </c>
       <c r="I88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="D89" s="16" t="n">
         <v>46178</v>
@@ -4160,33 +4420,36 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>incomprensible</t>
+          <t>exoneracion corte y reconexion</t>
         </is>
       </c>
       <c r="I89" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C90" s="7" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D90" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>mesa_3</t>
+          <t>mesa_4</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -4196,38 +4459,37 @@
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>Janet Villanueva</t>
-        </is>
-      </c>
-      <c r="H90" s="12" t="inlineStr">
-        <is>
-          <t>converzar</t>
-        </is>
-      </c>
+          <t>Liliana Mendoza</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr"/>
       <c r="I90" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D91" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>mesa_3</t>
+          <t>mesa_4</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -4237,31 +4499,30 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Janet Villanueva</t>
-        </is>
-      </c>
-      <c r="H91" s="12" t="inlineStr">
-        <is>
-          <t>exoneracion corte y reconexion</t>
-        </is>
-      </c>
+          <t>Liliana Mendoza</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr"/>
       <c r="I91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11A</t>
         </is>
       </c>
       <c r="C92" s="7" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D92" s="16" t="n">
         <v>46178</v>
@@ -4285,20 +4546,23 @@
       <c r="I92" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J92" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="D93" s="16" t="n">
         <v>46178</v>
@@ -4322,20 +4586,23 @@
       <c r="I93" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J93" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>11A</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C94" s="7" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D94" s="16" t="n">
         <v>46178</v>
@@ -4359,16 +4626,19 @@
       <c r="I94" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J94" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
@@ -4396,20 +4666,23 @@
       <c r="I95" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J95" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C96" s="7" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D96" s="16" t="n">
         <v>46178</v>
@@ -4433,20 +4706,23 @@
       <c r="I96" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J96" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="D97" s="16" t="n">
         <v>46178</v>
@@ -4470,20 +4746,23 @@
       <c r="I97" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J97" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C98" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D98" s="16" t="n">
         <v>46178</v>
@@ -4507,20 +4786,23 @@
       <c r="I98" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J98" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D99" s="16" t="n">
         <v>46178</v>
@@ -4544,20 +4826,23 @@
       <c r="I99" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J99" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C100" s="7" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D100" s="16" t="n">
         <v>46178</v>
@@ -4581,20 +4866,23 @@
       <c r="I100" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J100" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D101" s="16" t="n">
         <v>46178</v>
@@ -4618,20 +4906,23 @@
       <c r="I101" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J101" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="D102" s="16" t="n">
         <v>46178</v>
@@ -4655,11 +4946,14 @@
       <c r="I102" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J102" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -4668,7 +4962,7 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D103" s="16" t="n">
         <v>46178</v>
@@ -4692,20 +4986,23 @@
       <c r="I103" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J103" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D104" s="16" t="n">
         <v>46178</v>
@@ -4729,20 +5026,23 @@
       <c r="I104" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J104" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D105" s="16" t="n">
         <v>46178</v>
@@ -4766,20 +5066,23 @@
       <c r="I105" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J105" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D106" s="16" t="n">
         <v>46178</v>
@@ -4803,20 +5106,23 @@
       <c r="I106" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J106" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="D107" s="16" t="n">
         <v>46178</v>
@@ -4840,20 +5146,23 @@
       <c r="I107" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J107" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C108" s="7" t="n">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="D108" s="16" t="n">
         <v>46178</v>
@@ -4877,20 +5186,23 @@
       <c r="I108" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J108" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="D109" s="16" t="n">
         <v>46178</v>
@@ -4910,24 +5222,31 @@
           <t>Liliana Mendoza</t>
         </is>
       </c>
-      <c r="H109" s="12" t="inlineStr"/>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C110" s="7" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D110" s="16" t="n">
         <v>46178</v>
@@ -4951,20 +5270,23 @@
       <c r="I110" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J110" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D111" s="16" t="n">
         <v>46178</v>
@@ -4986,10 +5308,13 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>pago fraccionado</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5001,11 +5326,11 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C112" s="7" t="n">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="D112" s="16" t="n">
         <v>46178</v>
@@ -5029,11 +5354,14 @@
       <c r="I112" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J112" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
@@ -5042,7 +5370,7 @@
         </is>
       </c>
       <c r="C113" s="7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D113" s="16" t="n">
         <v>46178</v>
@@ -5062,28 +5390,27 @@
           <t>Liliana Mendoza</t>
         </is>
       </c>
-      <c r="H113" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H113" s="12" t="inlineStr"/>
       <c r="I113" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C114" s="7" t="n">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="D114" s="16" t="n">
         <v>46178</v>
@@ -5107,20 +5434,23 @@
       <c r="I114" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J114" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C115" s="7" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D115" s="16" t="n">
         <v>46178</v>
@@ -5144,20 +5474,23 @@
       <c r="I115" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J115" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C116" s="7" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="D116" s="16" t="n">
         <v>46178</v>
@@ -5181,20 +5514,23 @@
       <c r="I116" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J116" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C117" s="7" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D117" s="16" t="n">
         <v>46178</v>
@@ -5218,20 +5554,23 @@
       <c r="I117" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J117" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C118" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D118" s="16" t="n">
         <v>46178</v>
@@ -5255,20 +5594,23 @@
       <c r="I118" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J118" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D119" s="16" t="n">
         <v>46178</v>
@@ -5292,20 +5634,23 @@
       <c r="I119" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J119" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C120" s="7" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="D120" s="16" t="n">
         <v>46178</v>
@@ -5329,20 +5674,23 @@
       <c r="I120" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J120" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D121" s="16" t="n">
         <v>46178</v>
@@ -5366,20 +5714,23 @@
       <c r="I121" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J121" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C122" s="7" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D122" s="16" t="n">
         <v>46178</v>
@@ -5403,20 +5754,23 @@
       <c r="I122" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J122" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D123" s="16" t="n">
         <v>46178</v>
@@ -5440,20 +5794,23 @@
       <c r="I123" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J123" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C124" s="7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D124" s="16" t="n">
         <v>46178</v>
@@ -5477,20 +5834,23 @@
       <c r="I124" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J124" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D125" s="16" t="n">
         <v>46178</v>
@@ -5510,24 +5870,31 @@
           <t>Liliana Mendoza</t>
         </is>
       </c>
-      <c r="H125" s="12" t="inlineStr"/>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C126" s="7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D126" s="16" t="n">
         <v>46178</v>
@@ -5551,20 +5918,23 @@
       <c r="I126" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J126" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D127" s="16" t="n">
         <v>46178</v>
@@ -5590,22 +5960,25 @@
         </is>
       </c>
       <c r="I127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C128" s="7" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D128" s="16" t="n">
         <v>46178</v>
@@ -5625,31 +5998,38 @@
           <t>Liliana Mendoza</t>
         </is>
       </c>
-      <c r="H128" s="12" t="inlineStr"/>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C129" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D129" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>mesa_4</t>
+          <t>mesa_5</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
@@ -5659,38 +6039,37 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Liliana Mendoza</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr">
-        <is>
-          <t>pago fraccionado</t>
-        </is>
-      </c>
+          <t>Maximo Encarnacion</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr"/>
       <c r="I129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C130" s="7" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D130" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>mesa_4</t>
+          <t>mesa_5</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -5700,31 +6079,34 @@
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>Liliana Mendoza</t>
+          <t>Maximo Encarnacion</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>pago fraccionado</t>
+          <t>Exonerado</t>
         </is>
       </c>
       <c r="I130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C131" s="7" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D131" s="16" t="n">
         <v>46178</v>
@@ -5748,20 +6130,23 @@
       <c r="I131" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J131" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C132" s="7" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D132" s="16" t="n">
         <v>46178</v>
@@ -5781,28 +6166,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H132" s="12" t="inlineStr">
-        <is>
-          <t>Exonerado</t>
-        </is>
-      </c>
+      <c r="H132" s="12" t="inlineStr"/>
       <c r="I132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C133" s="7" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D133" s="16" t="n">
         <v>46178</v>
@@ -5826,20 +6210,23 @@
       <c r="I133" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J133" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C134" s="7" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="D134" s="16" t="n">
         <v>46178</v>
@@ -5863,20 +6250,23 @@
       <c r="I134" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J134" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C135" s="7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D135" s="16" t="n">
         <v>46178</v>
@@ -5896,24 +6286,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H135" s="12" t="inlineStr"/>
+      <c r="H135" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C136" s="7" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="D136" s="16" t="n">
         <v>46178</v>
@@ -5937,20 +6334,23 @@
       <c r="I136" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J136" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C137" s="7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D137" s="16" t="n">
         <v>46178</v>
@@ -5970,24 +6370,23 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H137" s="12" t="inlineStr">
-        <is>
-          <t>Numero</t>
-        </is>
-      </c>
+      <c r="H137" s="12" t="inlineStr"/>
       <c r="I137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C138" s="7" t="n">
@@ -6011,24 +6410,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H138" s="12" t="inlineStr"/>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D139" s="16" t="n">
         <v>46178</v>
@@ -6052,20 +6458,23 @@
       <c r="I139" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J139" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C140" s="7" t="n">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="D140" s="16" t="n">
         <v>46178</v>
@@ -6085,28 +6494,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H140" s="12" t="inlineStr">
-        <is>
-          <t>Numero</t>
-        </is>
-      </c>
+      <c r="H140" s="12" t="inlineStr"/>
       <c r="I140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C141" s="7" t="n">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="D141" s="16" t="n">
         <v>46178</v>
@@ -6126,24 +6534,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H141" s="12" t="inlineStr"/>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I141" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C142" s="7" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="D142" s="16" t="n">
         <v>46178</v>
@@ -6167,20 +6582,23 @@
       <c r="I142" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J142" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="D143" s="16" t="n">
         <v>46178</v>
@@ -6200,12 +6618,11 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H143" s="12" t="inlineStr">
-        <is>
-          <t>Numero</t>
-        </is>
-      </c>
+      <c r="H143" s="12" t="inlineStr"/>
       <c r="I143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6217,11 +6634,11 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C144" s="7" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="D144" s="16" t="n">
         <v>46178</v>
@@ -6245,20 +6662,23 @@
       <c r="I144" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J144" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C145" s="7" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D145" s="16" t="n">
         <v>46178</v>
@@ -6282,20 +6702,23 @@
       <c r="I145" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J145" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C146" s="7" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D146" s="16" t="n">
         <v>46178</v>
@@ -6315,24 +6738,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H146" s="12" t="inlineStr"/>
+      <c r="H146" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="D147" s="16" t="n">
         <v>46178</v>
@@ -6352,24 +6782,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H147" s="12" t="inlineStr"/>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C148" s="7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D148" s="16" t="n">
         <v>46178</v>
@@ -6389,28 +6826,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H148" s="12" t="inlineStr">
-        <is>
-          <t>Numero</t>
-        </is>
-      </c>
+      <c r="H148" s="12" t="inlineStr"/>
       <c r="I148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C149" s="7" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="D149" s="16" t="n">
         <v>46178</v>
@@ -6430,24 +6866,23 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H149" s="12" t="inlineStr">
-        <is>
-          <t>Numero</t>
-        </is>
-      </c>
+      <c r="H149" s="12" t="inlineStr"/>
       <c r="I149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="C150" s="7" t="n">
@@ -6471,24 +6906,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H150" s="12" t="inlineStr"/>
+      <c r="H150" s="12" t="inlineStr">
+        <is>
+          <t>Pago fraccionado</t>
+        </is>
+      </c>
       <c r="I150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D151" s="16" t="n">
         <v>46178</v>
@@ -6508,24 +6950,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H151" s="12" t="inlineStr"/>
+      <c r="H151" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C152" s="7" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D152" s="16" t="n">
         <v>46178</v>
@@ -6545,28 +6994,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H152" s="12" t="inlineStr">
-        <is>
-          <t>Pago fraccionado</t>
-        </is>
-      </c>
+      <c r="H152" s="12" t="inlineStr"/>
       <c r="I152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D153" s="16" t="n">
         <v>46178</v>
@@ -6588,26 +7036,29 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Numero</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C154" s="7" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D154" s="16" t="n">
         <v>46178</v>
@@ -6631,20 +7082,23 @@
       <c r="I154" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J154" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D155" s="16" t="n">
         <v>46178</v>
@@ -6664,28 +7118,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H155" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H155" s="12" t="inlineStr"/>
       <c r="I155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="C156" s="7" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D156" s="16" t="n">
         <v>46178</v>
@@ -6709,11 +7162,14 @@
       <c r="I156" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J156" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
@@ -6722,7 +7178,7 @@
         </is>
       </c>
       <c r="C157" s="7" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D157" s="16" t="n">
         <v>46178</v>
@@ -6742,24 +7198,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H157" s="12" t="inlineStr"/>
+      <c r="H157" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C158" s="7" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D158" s="16" t="n">
         <v>46178</v>
@@ -6783,20 +7246,23 @@
       <c r="I158" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J158" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C159" s="7" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D159" s="16" t="n">
         <v>46178</v>
@@ -6816,28 +7282,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H159" s="12" t="inlineStr">
-        <is>
-          <t>Numero</t>
-        </is>
-      </c>
+      <c r="H159" s="12" t="inlineStr"/>
       <c r="I159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C160" s="7" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D160" s="16" t="n">
         <v>46178</v>
@@ -6861,20 +7326,23 @@
       <c r="I160" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J160" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161" ht="18" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C161" s="7" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="D161" s="16" t="n">
         <v>46178</v>
@@ -6894,24 +7362,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H161" s="12" t="inlineStr"/>
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>Numero</t>
+        </is>
+      </c>
       <c r="I161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C162" s="7" t="n">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="D162" s="16" t="n">
         <v>46178</v>
@@ -6935,20 +7410,23 @@
       <c r="I162" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J162" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C163" s="7" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="D163" s="16" t="n">
         <v>46178</v>
@@ -6968,28 +7446,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H163" s="12" t="inlineStr">
-        <is>
-          <t>Numero</t>
-        </is>
-      </c>
+      <c r="H163" s="12" t="inlineStr"/>
       <c r="I163" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C164" s="7" t="n">
-        <v>157</v>
+        <v>11</v>
       </c>
       <c r="D164" s="16" t="n">
         <v>46178</v>
@@ -7013,20 +7490,23 @@
       <c r="I164" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J164" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C165" s="7" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D165" s="16" t="n">
         <v>46178</v>
@@ -7050,20 +7530,23 @@
       <c r="I165" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J165" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C166" s="7" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="D166" s="16" t="n">
         <v>46178</v>
@@ -7083,24 +7566,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H166" s="12" t="inlineStr"/>
+      <c r="H166" s="12" t="inlineStr">
+        <is>
+          <t>Pago para tanque + 200</t>
+        </is>
+      </c>
       <c r="I166" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J166" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C167" s="7" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="D167" s="16" t="n">
         <v>46178</v>
@@ -7120,8 +7610,15 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H167" s="12" t="inlineStr"/>
+      <c r="H167" s="12" t="inlineStr">
+        <is>
+          <t>Pago para tanque + 200</t>
+        </is>
+      </c>
       <c r="I167" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J167" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7133,11 +7630,11 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C168" s="7" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D168" s="16" t="n">
         <v>46178</v>
@@ -7157,31 +7654,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H168" s="12" t="inlineStr">
-        <is>
-          <t>Pago para tanque + 200</t>
-        </is>
-      </c>
+      <c r="H168" s="12" t="inlineStr"/>
       <c r="I168" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J168" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="C169" s="7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D169" s="16" t="n">
         <v>46178</v>
@@ -7201,31 +7694,27 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H169" s="12" t="inlineStr">
-        <is>
-          <t>Pago para tanque + 200</t>
-        </is>
-      </c>
+      <c r="H169" s="12" t="inlineStr"/>
       <c r="I169" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J169" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C170" s="7" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="D170" s="16" t="n">
         <v>46178</v>
@@ -7249,20 +7738,23 @@
       <c r="I170" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J170" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C171" s="7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D171" s="16" t="n">
         <v>46178</v>
@@ -7286,20 +7778,23 @@
       <c r="I171" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J171" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C172" s="7" t="n">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="D172" s="16" t="n">
         <v>46178</v>
@@ -7323,20 +7818,23 @@
       <c r="I172" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J172" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C173" s="7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D173" s="16" t="n">
         <v>46178</v>
@@ -7360,6 +7858,9 @@
       <c r="I173" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J173" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
@@ -7369,11 +7870,11 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C174" s="7" t="n">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="D174" s="16" t="n">
         <v>46178</v>
@@ -7397,20 +7898,23 @@
       <c r="I174" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J174" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C175" s="7" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D175" s="16" t="n">
         <v>46178</v>
@@ -7434,20 +7938,23 @@
       <c r="I175" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J175" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C176" s="7" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D176" s="16" t="n">
         <v>46178</v>
@@ -7471,20 +7978,23 @@
       <c r="I176" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J176" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C177" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D177" s="16" t="n">
         <v>46178</v>
@@ -7508,20 +8018,23 @@
       <c r="I177" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J177" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C178" s="7" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D178" s="16" t="n">
         <v>46178</v>
@@ -7545,20 +8058,23 @@
       <c r="I178" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J178" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C179" s="7" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D179" s="16" t="n">
         <v>46178</v>
@@ -7582,20 +8098,23 @@
       <c r="I179" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J179" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C180" s="7" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D180" s="16" t="n">
         <v>46178</v>
@@ -7619,20 +8138,23 @@
       <c r="I180" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J180" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C181" s="7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D181" s="16" t="n">
         <v>46178</v>
@@ -7656,20 +8178,23 @@
       <c r="I181" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J181" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C182" s="7" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D182" s="16" t="n">
         <v>46178</v>
@@ -7693,20 +8218,23 @@
       <c r="I182" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J182" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C183" s="7" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D183" s="16" t="n">
         <v>46178</v>
@@ -7730,20 +8258,23 @@
       <c r="I183" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J183" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C184" s="7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D184" s="16" t="n">
         <v>46178</v>
@@ -7767,20 +8298,23 @@
       <c r="I184" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J184" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="185" ht="18" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C185" s="7" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D185" s="16" t="n">
         <v>46178</v>
@@ -7804,20 +8338,23 @@
       <c r="I185" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J185" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C186" s="7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D186" s="16" t="n">
         <v>46178</v>
@@ -7841,20 +8378,23 @@
       <c r="I186" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J186" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C187" s="7" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="D187" s="16" t="n">
         <v>46178</v>
@@ -7878,20 +8418,23 @@
       <c r="I187" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J187" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C188" s="7" t="n">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D188" s="16" t="n">
         <v>46178</v>
@@ -7915,20 +8458,23 @@
       <c r="I188" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J188" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C189" s="7" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="D189" s="16" t="n">
         <v>46178</v>
@@ -7952,20 +8498,23 @@
       <c r="I189" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J189" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C190" s="7" t="n">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="D190" s="16" t="n">
         <v>46178</v>
@@ -7989,20 +8538,23 @@
       <c r="I190" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J190" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C191" s="7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D191" s="16" t="n">
         <v>46178</v>
@@ -8026,20 +8578,23 @@
       <c r="I191" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J191" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C192" s="7" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D192" s="16" t="n">
         <v>46178</v>
@@ -8063,20 +8618,23 @@
       <c r="I192" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J192" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C193" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D193" s="16" t="n">
         <v>46178</v>
@@ -8100,20 +8658,23 @@
       <c r="I193" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J193" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C194" s="7" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="D194" s="16" t="n">
         <v>46178</v>
@@ -8137,20 +8698,23 @@
       <c r="I194" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J194" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C195" s="7" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D195" s="16" t="n">
         <v>46178</v>
@@ -8174,20 +8738,23 @@
       <c r="I195" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J195" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C196" s="7" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D196" s="16" t="n">
         <v>46178</v>
@@ -8211,6 +8778,9 @@
       <c r="I196" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J196" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
@@ -8220,11 +8790,11 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C197" s="7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D197" s="16" t="n">
         <v>46178</v>
@@ -8248,20 +8818,23 @@
       <c r="I197" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J197" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C198" s="7" t="n">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="D198" s="16" t="n">
         <v>46178</v>
@@ -8285,20 +8858,23 @@
       <c r="I198" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J198" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C199" s="7" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="D199" s="16" t="n">
         <v>46178</v>
@@ -8322,20 +8898,23 @@
       <c r="I199" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J199" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C200" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D200" s="16" t="n">
         <v>46178</v>
@@ -8359,16 +8938,19 @@
       <c r="I200" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J200" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C201" s="7" t="n">
@@ -8396,20 +8978,23 @@
       <c r="I201" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J201" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C202" s="7" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="D202" s="16" t="n">
         <v>46178</v>
@@ -8433,20 +9018,23 @@
       <c r="I202" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J202" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C203" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D203" s="16" t="n">
         <v>46178</v>
@@ -8470,20 +9058,23 @@
       <c r="I203" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J203" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C204" s="7" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D204" s="16" t="n">
         <v>46178</v>
@@ -8507,11 +9098,14 @@
       <c r="I204" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J204" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -8520,7 +9114,7 @@
         </is>
       </c>
       <c r="C205" s="7" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D205" s="16" t="n">
         <v>46178</v>
@@ -8544,20 +9138,23 @@
       <c r="I205" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J205" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C206" s="7" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="D206" s="16" t="n">
         <v>46178</v>
@@ -8581,20 +9178,23 @@
       <c r="I206" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J206" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C207" s="7" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D207" s="16" t="n">
         <v>46178</v>
@@ -8618,20 +9218,23 @@
       <c r="I207" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J207" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C208" s="7" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D208" s="16" t="n">
         <v>46178</v>
@@ -8655,20 +9258,23 @@
       <c r="I208" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J208" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C209" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D209" s="16" t="n">
         <v>46178</v>
@@ -8692,20 +9298,23 @@
       <c r="I209" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J209" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C210" s="7" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D210" s="16" t="n">
         <v>46178</v>
@@ -8729,20 +9338,23 @@
       <c r="I210" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J210" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C211" s="7" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D211" s="16" t="n">
         <v>46178</v>
@@ -8766,20 +9378,23 @@
       <c r="I211" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J211" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C212" s="7" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D212" s="16" t="n">
         <v>46178</v>
@@ -8803,20 +9418,23 @@
       <c r="I212" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J212" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C213" s="7" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D213" s="16" t="n">
         <v>46178</v>
@@ -8840,20 +9458,23 @@
       <c r="I213" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J213" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C214" s="7" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D214" s="16" t="n">
         <v>46178</v>
@@ -8877,20 +9498,23 @@
       <c r="I214" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J214" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C215" s="7" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D215" s="16" t="n">
         <v>46178</v>
@@ -8914,20 +9538,23 @@
       <c r="I215" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J215" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C216" s="7" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D216" s="16" t="n">
         <v>46178</v>
@@ -8951,20 +9578,23 @@
       <c r="I216" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J216" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C217" s="7" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="D217" s="16" t="n">
         <v>46178</v>
@@ -8988,20 +9618,23 @@
       <c r="I217" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J217" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C218" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D218" s="16" t="n">
         <v>46178</v>
@@ -9025,20 +9658,23 @@
       <c r="I218" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J218" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C219" s="7" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D219" s="16" t="n">
         <v>46178</v>
@@ -9062,20 +9698,23 @@
       <c r="I219" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J219" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C220" s="7" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D220" s="16" t="n">
         <v>46178</v>
@@ -9099,11 +9738,14 @@
       <c r="I220" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J220" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
@@ -9112,7 +9754,7 @@
         </is>
       </c>
       <c r="C221" s="7" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D221" s="16" t="n">
         <v>46178</v>
@@ -9136,20 +9778,23 @@
       <c r="I221" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J221" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C222" s="7" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D222" s="16" t="n">
         <v>46178</v>
@@ -9173,20 +9818,23 @@
       <c r="I222" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J222" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C223" s="7" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D223" s="16" t="n">
         <v>46178</v>
@@ -9210,20 +9858,23 @@
       <c r="I223" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J223" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C224" s="7" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D224" s="16" t="n">
         <v>46178</v>
@@ -9247,20 +9898,23 @@
       <c r="I224" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J224" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C225" s="7" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D225" s="16" t="n">
         <v>46178</v>
@@ -9284,20 +9938,23 @@
       <c r="I225" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J225" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C226" s="7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D226" s="16" t="n">
         <v>46178</v>
@@ -9321,20 +9978,23 @@
       <c r="I226" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J226" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C227" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D227" s="16" t="n">
         <v>46178</v>
@@ -9358,20 +10018,23 @@
       <c r="I227" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J227" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C228" s="7" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="D228" s="16" t="n">
         <v>46178</v>
@@ -9395,20 +10058,23 @@
       <c r="I228" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J228" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C229" s="7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D229" s="16" t="n">
         <v>46178</v>
@@ -9432,20 +10098,23 @@
       <c r="I229" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J229" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C230" s="7" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D230" s="16" t="n">
         <v>46178</v>
@@ -9469,16 +10138,19 @@
       <c r="I230" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J230" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C231" s="7" t="n">
@@ -9506,20 +10178,23 @@
       <c r="I231" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J231" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C232" s="7" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="D232" s="16" t="n">
         <v>46178</v>
@@ -9543,20 +10218,23 @@
       <c r="I232" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J232" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C233" s="7" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D233" s="16" t="n">
         <v>46178</v>
@@ -9580,20 +10258,23 @@
       <c r="I233" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J233" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C234" s="7" t="n">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="D234" s="16" t="n">
         <v>46178</v>
@@ -9617,20 +10298,23 @@
       <c r="I234" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J234" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C235" s="7" t="n">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="D235" s="16" t="n">
         <v>46178</v>
@@ -9654,20 +10338,23 @@
       <c r="I235" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J235" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="C236" s="7" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D236" s="16" t="n">
         <v>46178</v>
@@ -9691,20 +10378,23 @@
       <c r="I236" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J236" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C237" s="7" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D237" s="16" t="n">
         <v>46178</v>
@@ -9728,20 +10418,23 @@
       <c r="I237" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J237" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="238" ht="18" customHeight="1">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C238" s="7" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="D238" s="16" t="n">
         <v>46178</v>
@@ -9765,16 +10458,19 @@
       <c r="I238" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J238" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="239" ht="18" customHeight="1">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C239" s="7" t="n">
@@ -9802,20 +10498,23 @@
       <c r="I239" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J239" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21A</t>
         </is>
       </c>
       <c r="C240" s="7" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D240" s="16" t="n">
         <v>46178</v>
@@ -9839,20 +10538,23 @@
       <c r="I240" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J240" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C241" s="7" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="D241" s="16" t="n">
         <v>46178</v>
@@ -9872,24 +10574,31 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H241" s="12" t="inlineStr"/>
+      <c r="H241" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I241" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J241" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>21A</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C242" s="7" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D242" s="16" t="n">
         <v>46178</v>
@@ -9913,23 +10622,26 @@
       <c r="I242" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J242" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C243" s="7" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D243" s="16" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
@@ -9946,12 +10658,11 @@
           <t>Maximo Encarnacion</t>
         </is>
       </c>
-      <c r="H243" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H243" s="12" t="inlineStr"/>
       <c r="I243" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J243" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9963,14 +10674,14 @@
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C244" s="7" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D244" s="16" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
@@ -9991,20 +10702,23 @@
       <c r="I244" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J244" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C245" s="7" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D245" s="16" t="n">
         <v>46179</v>
@@ -10028,16 +10742,19 @@
       <c r="I245" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J245" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C246" s="7" t="n">
@@ -10065,20 +10782,23 @@
       <c r="I246" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J246" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C247" s="7" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="D247" s="16" t="n">
         <v>46179</v>
@@ -10102,20 +10822,23 @@
       <c r="I247" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J247" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C248" s="7" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="D248" s="16" t="n">
         <v>46179</v>
@@ -10139,20 +10862,23 @@
       <c r="I248" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J248" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C249" s="7" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D249" s="16" t="n">
         <v>46179</v>
@@ -10176,20 +10902,23 @@
       <c r="I249" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J249" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C250" s="7" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D250" s="16" t="n">
         <v>46179</v>
@@ -10213,20 +10942,23 @@
       <c r="I250" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J250" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C251" s="7" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D251" s="16" t="n">
         <v>46179</v>
@@ -10250,20 +10982,23 @@
       <c r="I251" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J251" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C252" s="7" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D252" s="16" t="n">
         <v>46179</v>
@@ -10287,20 +11022,23 @@
       <c r="I252" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J252" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C253" s="7" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D253" s="16" t="n">
         <v>46179</v>
@@ -10324,20 +11062,23 @@
       <c r="I253" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J253" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C254" s="7" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="D254" s="16" t="n">
         <v>46179</v>
@@ -10361,20 +11102,23 @@
       <c r="I254" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J254" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C255" s="7" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D255" s="16" t="n">
         <v>46179</v>
@@ -10398,20 +11142,23 @@
       <c r="I255" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J255" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C256" s="7" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D256" s="16" t="n">
         <v>46179</v>
@@ -10435,20 +11182,23 @@
       <c r="I256" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J256" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C257" s="7" t="n">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D257" s="16" t="n">
         <v>46179</v>
@@ -10472,20 +11222,23 @@
       <c r="I257" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J257" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C258" s="7" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="D258" s="16" t="n">
         <v>46179</v>
@@ -10509,11 +11262,14 @@
       <c r="I258" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J258" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -10522,7 +11278,7 @@
         </is>
       </c>
       <c r="C259" s="7" t="n">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D259" s="16" t="n">
         <v>46179</v>
@@ -10546,20 +11302,23 @@
       <c r="I259" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J259" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C260" s="7" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D260" s="16" t="n">
         <v>46179</v>
@@ -10583,11 +11342,14 @@
       <c r="I260" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J260" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -10596,7 +11358,7 @@
         </is>
       </c>
       <c r="C261" s="7" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="D261" s="16" t="n">
         <v>46179</v>
@@ -10620,20 +11382,23 @@
       <c r="I261" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J261" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="C262" s="7" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D262" s="16" t="n">
         <v>46179</v>
@@ -10657,20 +11422,23 @@
       <c r="I262" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J262" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C263" s="7" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D263" s="16" t="n">
         <v>46179</v>
@@ -10694,20 +11462,23 @@
       <c r="I263" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J263" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C264" s="7" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D264" s="16" t="n">
         <v>46179</v>
@@ -10731,20 +11502,23 @@
       <c r="I264" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J264" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C265" s="7" t="n">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="D265" s="16" t="n">
         <v>46179</v>
@@ -10768,20 +11542,23 @@
       <c r="I265" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J265" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="C266" s="7" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="D266" s="16" t="n">
         <v>46179</v>
@@ -10805,20 +11582,23 @@
       <c r="I266" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J266" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C267" s="7" t="n">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="D267" s="16" t="n">
         <v>46179</v>
@@ -10842,20 +11622,23 @@
       <c r="I267" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J267" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C268" s="7" t="n">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="D268" s="16" t="n">
         <v>46179</v>
@@ -10879,20 +11662,23 @@
       <c r="I268" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J268" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C269" s="7" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D269" s="16" t="n">
         <v>46179</v>
@@ -10916,20 +11702,23 @@
       <c r="I269" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J269" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C270" s="7" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D270" s="16" t="n">
         <v>46179</v>
@@ -10953,20 +11742,23 @@
       <c r="I270" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J270" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="271" ht="18" customHeight="1">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C271" s="7" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="D271" s="16" t="n">
         <v>46179</v>
@@ -10990,20 +11782,23 @@
       <c r="I271" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J271" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C272" s="7" t="n">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="D272" s="16" t="n">
         <v>46179</v>
@@ -11027,20 +11822,23 @@
       <c r="I272" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J272" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C273" s="7" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="D273" s="16" t="n">
         <v>46179</v>
@@ -11064,20 +11862,23 @@
       <c r="I273" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J273" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C274" s="7" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D274" s="16" t="n">
         <v>46179</v>
@@ -11101,20 +11902,23 @@
       <c r="I274" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J274" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C275" s="7" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D275" s="16" t="n">
         <v>46179</v>
@@ -11138,20 +11942,23 @@
       <c r="I275" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J275" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C276" s="7" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="D276" s="16" t="n">
         <v>46179</v>
@@ -11175,27 +11982,30 @@
       <c r="I276" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J276" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C277" s="7" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D277" s="16" t="n">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>mesa_5</t>
+          <t>mesa_6</t>
         </is>
       </c>
       <c r="F277" s="10" t="inlineStr">
@@ -11205,34 +12015,41 @@
       </c>
       <c r="G277" s="11" t="inlineStr">
         <is>
-          <t>Maximo Encarnacion</t>
-        </is>
-      </c>
-      <c r="H277" s="12" t="inlineStr"/>
+          <t>Wagner Trujillo</t>
+        </is>
+      </c>
+      <c r="H277" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado + exoneracion</t>
+        </is>
+      </c>
       <c r="I277" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C278" s="7" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="D278" s="16" t="n">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>mesa_5</t>
+          <t>mesa_6</t>
         </is>
       </c>
       <c r="F278" s="10" t="inlineStr">
@@ -11242,27 +12059,30 @@
       </c>
       <c r="G278" s="11" t="inlineStr">
         <is>
-          <t>Maximo Encarnacion</t>
+          <t>Wagner Trujillo</t>
         </is>
       </c>
       <c r="H278" s="12" t="inlineStr"/>
       <c r="I278" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J278" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C279" s="7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D279" s="16" t="n">
         <v>46178</v>
@@ -11282,28 +12102,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H279" s="12" t="inlineStr">
-        <is>
-          <t>pago fraccionado + exoneracion</t>
-        </is>
-      </c>
+      <c r="H279" s="12" t="inlineStr"/>
       <c r="I279" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J279" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="1">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C280" s="7" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D280" s="16" t="n">
         <v>46178</v>
@@ -11323,24 +12142,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H280" s="12" t="inlineStr"/>
+      <c r="H280" s="12" t="inlineStr">
+        <is>
+          <t>60?</t>
+        </is>
+      </c>
       <c r="I280" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J280" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C281" s="7" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="D281" s="16" t="n">
         <v>46178</v>
@@ -11360,24 +12186,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H281" s="12" t="inlineStr"/>
+      <c r="H281" s="12" t="inlineStr">
+        <is>
+          <t>Ocaña?</t>
+        </is>
+      </c>
       <c r="I281" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J281" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16A</t>
         </is>
       </c>
       <c r="C282" s="7" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D282" s="16" t="n">
         <v>46178</v>
@@ -11397,28 +12230,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H282" s="12" t="inlineStr">
-        <is>
-          <t>60?</t>
-        </is>
-      </c>
+      <c r="H282" s="12" t="inlineStr"/>
       <c r="I282" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C283" s="7" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="D283" s="16" t="n">
         <v>46178</v>
@@ -11438,31 +12270,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H283" s="12" t="inlineStr">
-        <is>
-          <t>Ocaña?</t>
-        </is>
-      </c>
+      <c r="H283" s="12" t="inlineStr"/>
       <c r="I283" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J283" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>16A</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C284" s="7" t="n">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="D284" s="16" t="n">
         <v>46178</v>
@@ -11482,24 +12310,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H284" s="12" t="inlineStr"/>
+      <c r="H284" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I284" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J284" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C285" s="7" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="D285" s="16" t="n">
         <v>46178</v>
@@ -11523,20 +12358,23 @@
       <c r="I285" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J285" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="286" ht="18" customHeight="1">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C286" s="7" t="n">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D286" s="16" t="n">
         <v>46178</v>
@@ -11556,19 +12394,18 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H286" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H286" s="12" t="inlineStr"/>
       <c r="I286" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J286" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
@@ -11577,7 +12414,7 @@
         </is>
       </c>
       <c r="C287" s="7" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D287" s="16" t="n">
         <v>46178</v>
@@ -11597,24 +12434,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H287" s="12" t="inlineStr"/>
+      <c r="H287" s="12" t="inlineStr">
+        <is>
+          <t>Mz A?</t>
+        </is>
+      </c>
       <c r="I287" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J287" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="1">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27A</t>
         </is>
       </c>
       <c r="C288" s="7" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D288" s="16" t="n">
         <v>46178</v>
@@ -11638,20 +12482,23 @@
       <c r="I288" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J288" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="289" ht="18" customHeight="1">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C289" s="7" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D289" s="16" t="n">
         <v>46178</v>
@@ -11671,28 +12518,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H289" s="12" t="inlineStr">
-        <is>
-          <t>Mz A?</t>
-        </is>
-      </c>
+      <c r="H289" s="12" t="inlineStr"/>
       <c r="I289" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J289" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="1">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>27A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C290" s="7" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D290" s="16" t="n">
         <v>46178</v>
@@ -11716,20 +12562,23 @@
       <c r="I290" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J290" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="291" ht="18" customHeight="1">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C291" s="7" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D291" s="16" t="n">
         <v>46178</v>
@@ -11753,20 +12602,23 @@
       <c r="I291" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J291" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="292" ht="18" customHeight="1">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C292" s="7" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D292" s="16" t="n">
         <v>46178</v>
@@ -11790,6 +12642,9 @@
       <c r="I292" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J292" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="293" ht="18" customHeight="1">
       <c r="A293" s="6" t="inlineStr">
@@ -11799,11 +12654,11 @@
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C293" s="7" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="D293" s="16" t="n">
         <v>46178</v>
@@ -11827,20 +12682,23 @@
       <c r="I293" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J293" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="294" ht="18" customHeight="1">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C294" s="7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D294" s="16" t="n">
         <v>46178</v>
@@ -11864,20 +12722,23 @@
       <c r="I294" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J294" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="295" ht="18" customHeight="1">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C295" s="7" t="n">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="D295" s="16" t="n">
         <v>46178</v>
@@ -11901,20 +12762,23 @@
       <c r="I295" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J295" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="296" ht="18" customHeight="1">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C296" s="7" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D296" s="16" t="n">
         <v>46178</v>
@@ -11938,20 +12802,23 @@
       <c r="I296" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J296" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="297" ht="18" customHeight="1">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C297" s="7" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D297" s="16" t="n">
         <v>46178</v>
@@ -11975,20 +12842,23 @@
       <c r="I297" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J297" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="298" ht="18" customHeight="1">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C298" s="7" t="n">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D298" s="16" t="n">
         <v>46178</v>
@@ -12012,20 +12882,23 @@
       <c r="I298" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J298" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="299" ht="18" customHeight="1">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C299" s="7" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D299" s="16" t="n">
         <v>46178</v>
@@ -12049,23 +12922,26 @@
       <c r="I299" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J299" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C300" s="7" t="n">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="D300" s="16" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
@@ -12082,27 +12958,34 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H300" s="12" t="inlineStr"/>
+      <c r="H300" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I300" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J300" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="1">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C301" s="7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D301" s="16" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
@@ -12123,20 +13006,23 @@
       <c r="I301" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J301" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="302" ht="18" customHeight="1">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C302" s="7" t="n">
-        <v>8</v>
+        <v>383</v>
       </c>
       <c r="D302" s="16" t="n">
         <v>46179</v>
@@ -12156,28 +13042,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H302" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H302" s="12" t="inlineStr"/>
       <c r="I302" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J302" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="1">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C303" s="7" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D303" s="16" t="n">
         <v>46179</v>
@@ -12201,20 +13086,23 @@
       <c r="I303" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J303" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="304" ht="18" customHeight="1">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C304" s="7" t="n">
-        <v>383</v>
+        <v>62</v>
       </c>
       <c r="D304" s="16" t="n">
         <v>46179</v>
@@ -12238,20 +13126,23 @@
       <c r="I304" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J304" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="305" ht="18" customHeight="1">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B305" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C305" s="7" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D305" s="16" t="n">
         <v>46179</v>
@@ -12271,24 +13162,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H305" s="12" t="inlineStr"/>
+      <c r="H305" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I305" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J305" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="1">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C306" s="7" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D306" s="16" t="n">
         <v>46179</v>
@@ -12312,20 +13210,23 @@
       <c r="I306" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J306" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="307" ht="18" customHeight="1">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B307" s="6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C307" s="7" t="n">
-        <v>58</v>
+        <v>208</v>
       </c>
       <c r="D307" s="16" t="n">
         <v>46179</v>
@@ -12347,26 +13248,29 @@
       </c>
       <c r="H307" s="12" t="inlineStr">
         <is>
-          <t>reclamo</t>
+          <t>consumo +200 tanque</t>
         </is>
       </c>
       <c r="I307" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J307" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="1">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C308" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D308" s="16" t="n">
         <v>46179</v>
@@ -12390,20 +13294,23 @@
       <c r="I308" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J308" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="309" ht="18" customHeight="1">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B309" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C309" s="7" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="D309" s="16" t="n">
         <v>46179</v>
@@ -12423,28 +13330,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H309" s="12" t="inlineStr">
-        <is>
-          <t>consumo +200 tanque</t>
-        </is>
-      </c>
+      <c r="H309" s="12" t="inlineStr"/>
       <c r="I309" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J309" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="1">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C310" s="7" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D310" s="16" t="n">
         <v>46179</v>
@@ -12468,20 +13374,23 @@
       <c r="I310" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J310" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="311" ht="18" customHeight="1">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C311" s="7" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="D311" s="16" t="n">
         <v>46179</v>
@@ -12505,20 +13414,23 @@
       <c r="I311" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J311" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="312" ht="18" customHeight="1">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C312" s="7" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D312" s="16" t="n">
         <v>46179</v>
@@ -12542,20 +13454,23 @@
       <c r="I312" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J312" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C313" s="7" t="n">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="D313" s="16" t="n">
         <v>46179</v>
@@ -12579,20 +13494,23 @@
       <c r="I313" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J313" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="314" ht="18" customHeight="1">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C314" s="7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D314" s="16" t="n">
         <v>46179</v>
@@ -12612,24 +13530,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H314" s="12" t="inlineStr"/>
+      <c r="H314" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I314" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J314" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="1">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C315" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D315" s="16" t="n">
         <v>46179</v>
@@ -12653,20 +13578,23 @@
       <c r="I315" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J315" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="316" ht="18" customHeight="1">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C316" s="7" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D316" s="16" t="n">
         <v>46179</v>
@@ -12686,28 +13614,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H316" s="12" t="inlineStr">
-        <is>
-          <t>pago fraccionado</t>
-        </is>
-      </c>
+      <c r="H316" s="12" t="inlineStr"/>
       <c r="I316" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J316" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="1">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B317" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C317" s="7" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D317" s="16" t="n">
         <v>46179</v>
@@ -12731,20 +13658,23 @@
       <c r="I317" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J317" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="318" ht="18" customHeight="1">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C318" s="7" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D318" s="16" t="n">
         <v>46179</v>
@@ -12764,15 +13694,22 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H318" s="12" t="inlineStr"/>
+      <c r="H318" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I318" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J318" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B319" s="6" t="inlineStr">
@@ -12781,7 +13718,7 @@
         </is>
       </c>
       <c r="C319" s="7" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="D319" s="16" t="n">
         <v>46179</v>
@@ -12801,24 +13738,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H319" s="12" t="inlineStr"/>
+      <c r="H319" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I319" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J319" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="1">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C320" s="7" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D320" s="16" t="n">
         <v>46179</v>
@@ -12838,12 +13782,11 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H320" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H320" s="12" t="inlineStr"/>
       <c r="I320" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J320" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12855,11 +13798,11 @@
       </c>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C321" s="7" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D321" s="16" t="n">
         <v>46179</v>
@@ -12887,20 +13830,23 @@
       <c r="I321" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J321" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="322" ht="18" customHeight="1">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C322" s="7" t="n">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="D322" s="16" t="n">
         <v>46179</v>
@@ -12924,20 +13870,23 @@
       <c r="I322" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J322" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="323" ht="18" customHeight="1">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C323" s="7" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D323" s="16" t="n">
         <v>46179</v>
@@ -12957,28 +13906,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H323" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H323" s="12" t="inlineStr"/>
       <c r="I323" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J323" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="1">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C324" s="7" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D324" s="16" t="n">
         <v>46179</v>
@@ -13002,20 +13950,23 @@
       <c r="I324" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J324" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="325" ht="18" customHeight="1">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C325" s="7" t="n">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="D325" s="16" t="n">
         <v>46179</v>
@@ -13039,20 +13990,23 @@
       <c r="I325" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J325" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="326" ht="18" customHeight="1">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C326" s="7" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="D326" s="16" t="n">
         <v>46179</v>
@@ -13076,20 +14030,23 @@
       <c r="I326" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J326" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="327" ht="18" customHeight="1">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C327" s="7" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D327" s="16" t="n">
         <v>46179</v>
@@ -13113,20 +14070,23 @@
       <c r="I327" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J327" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="328" ht="18" customHeight="1">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C328" s="7" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="D328" s="16" t="n">
         <v>46179</v>
@@ -13150,20 +14110,23 @@
       <c r="I328" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J328" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="329" ht="18" customHeight="1">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C329" s="7" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="D329" s="16" t="n">
         <v>46179</v>
@@ -13183,24 +14146,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H329" s="12" t="inlineStr"/>
+      <c r="H329" s="12" t="inlineStr">
+        <is>
+          <t>exoneracion</t>
+        </is>
+      </c>
       <c r="I329" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J329" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="330" ht="18" customHeight="1">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C330" s="7" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D330" s="16" t="n">
         <v>46179</v>
@@ -13224,23 +14194,26 @@
       <c r="I330" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J330" s="17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="331" ht="18" customHeight="1">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B331" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C331" s="7" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D331" s="16" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
@@ -13257,31 +14230,30 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H331" s="12" t="inlineStr">
-        <is>
-          <t>exoneracion</t>
-        </is>
-      </c>
+      <c r="H331" s="12" t="inlineStr"/>
       <c r="I331" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J331" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="332" ht="18" customHeight="1">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C332" s="7" t="n">
-        <v>33</v>
+        <v>177</v>
       </c>
       <c r="D332" s="16" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
@@ -13300,22 +14272,25 @@
       </c>
       <c r="H332" s="12" t="inlineStr"/>
       <c r="I332" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J332" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="333" ht="18" customHeight="1">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C333" s="7" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="D333" s="16" t="n">
         <v>46183</v>
@@ -13340,22 +14315,22 @@
         <v>4</v>
       </c>
       <c r="J333" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" ht="18" customHeight="1">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C334" s="7" t="n">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="D334" s="16" t="n">
         <v>46183</v>
@@ -13380,22 +14355,22 @@
         <v>4</v>
       </c>
       <c r="J334" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" ht="18" customHeight="1">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C335" s="7" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="D335" s="16" t="n">
         <v>46183</v>
@@ -13415,27 +14390,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H335" s="12" t="inlineStr"/>
+      <c r="H335" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I335" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J335" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" ht="18" customHeight="1">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C336" s="7" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="D336" s="16" t="n">
         <v>46183</v>
@@ -13455,27 +14434,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H336" s="12" t="inlineStr"/>
+      <c r="H336" s="12" t="inlineStr">
+        <is>
+          <t>pago fraccionado</t>
+        </is>
+      </c>
       <c r="I336" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J336" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337" ht="18" customHeight="1">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C337" s="7" t="n">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="D337" s="16" t="n">
         <v>46183</v>
@@ -13497,29 +14480,29 @@
       </c>
       <c r="H337" s="12" t="inlineStr">
         <is>
-          <t>pago fraccionado</t>
+          <t>reclamo</t>
         </is>
       </c>
       <c r="I337" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J337" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338" ht="18" customHeight="1">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C338" s="7" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="D338" s="16" t="n">
         <v>46183</v>
@@ -13539,31 +14522,27 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H338" s="12" t="inlineStr">
-        <is>
-          <t>pago fraccionado</t>
-        </is>
-      </c>
+      <c r="H338" s="12" t="inlineStr"/>
       <c r="I338" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J338" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" ht="18" customHeight="1">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C339" s="7" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="D339" s="16" t="n">
         <v>46183</v>
@@ -13592,22 +14571,22 @@
         <v>4</v>
       </c>
       <c r="J339" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" ht="18" customHeight="1">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C340" s="7" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D340" s="16" t="n">
         <v>46183</v>
@@ -13627,27 +14606,31 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H340" s="12" t="inlineStr"/>
+      <c r="H340" s="12" t="inlineStr">
+        <is>
+          <t>exonerado</t>
+        </is>
+      </c>
       <c r="I340" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J340" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" ht="18" customHeight="1">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C341" s="7" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="D341" s="16" t="n">
         <v>46183</v>
@@ -13667,106 +14650,106 @@
           <t>Wagner Trujillo</t>
         </is>
       </c>
-      <c r="H341" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+      <c r="H341" s="12" t="inlineStr"/>
       <c r="I341" s="10" t="n">
         <v>4</v>
       </c>
       <c r="J341" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" ht="18" customHeight="1">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C342" s="7" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D342" s="16" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>mesa_6</t>
+          <t>mesa_2</t>
         </is>
       </c>
       <c r="F342" s="10" t="inlineStr">
         <is>
-          <t>solo_un_cobrador</t>
+          <t>multi_mesa_resuelta</t>
         </is>
       </c>
       <c r="G342" s="11" t="inlineStr">
         <is>
-          <t>Wagner Trujillo</t>
+          <t>Yerald Romero</t>
         </is>
       </c>
       <c r="H342" s="12" t="inlineStr">
         <is>
-          <t>exonerado</t>
+          <t>Exoneracion</t>
         </is>
       </c>
       <c r="I342" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J342" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" ht="18" customHeight="1">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C343" s="7" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D343" s="16" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>mesa_6</t>
+          <t>mesa_3</t>
         </is>
       </c>
       <c r="F343" s="10" t="inlineStr">
         <is>
-          <t>solo_un_cobrador</t>
+          <t>multi_mesa_resuelta</t>
         </is>
       </c>
       <c r="G343" s="11" t="inlineStr">
         <is>
-          <t>Wagner Trujillo</t>
-        </is>
-      </c>
-      <c r="H343" s="12" t="inlineStr"/>
+          <t>Janet Villanueva</t>
+        </is>
+      </c>
+      <c r="H343" s="12" t="inlineStr">
+        <is>
+          <t>reclamo</t>
+        </is>
+      </c>
       <c r="I343" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J343" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" ht="18" customHeight="1">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B344" s="6" t="inlineStr">
@@ -13775,14 +14758,14 @@
         </is>
       </c>
       <c r="C344" s="7" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D344" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>mesa_2</t>
+          <t>mesa_3</t>
         </is>
       </c>
       <c r="F344" s="10" t="inlineStr">
@@ -13792,16 +14775,19 @@
       </c>
       <c r="G344" s="11" t="inlineStr">
         <is>
-          <t>Yerald Romero</t>
+          <t>Janet Villanueva</t>
         </is>
       </c>
       <c r="H344" s="12" t="inlineStr">
         <is>
-          <t>Exoneracion</t>
+          <t>pago fraccionado</t>
         </is>
       </c>
       <c r="I344" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="J344" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="345" ht="18" customHeight="1">
@@ -13812,18 +14798,18 @@
       </c>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C345" s="7" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D345" s="16" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>mesa_3</t>
+          <t>mesa_5</t>
         </is>
       </c>
       <c r="F345" s="10" t="inlineStr">
@@ -13833,19 +14819,15 @@
       </c>
       <c r="G345" s="11" t="inlineStr">
         <is>
-          <t>Janet Villanueva</t>
-        </is>
-      </c>
-      <c r="H345" s="12" t="inlineStr">
-        <is>
-          <t>reclamo</t>
-        </is>
-      </c>
+          <t>Maximo Encarnacion</t>
+        </is>
+      </c>
+      <c r="H345" s="12" t="inlineStr"/>
       <c r="I345" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J345" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346" ht="18" customHeight="1">
@@ -13860,14 +14842,14 @@
         </is>
       </c>
       <c r="C346" s="7" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D346" s="16" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>mesa_3</t>
+          <t>mesa_5</t>
         </is>
       </c>
       <c r="F346" s="10" t="inlineStr">
@@ -13877,19 +14859,15 @@
       </c>
       <c r="G346" s="11" t="inlineStr">
         <is>
-          <t>Janet Villanueva</t>
-        </is>
-      </c>
-      <c r="H346" s="12" t="inlineStr">
-        <is>
-          <t>pago fraccionado</t>
-        </is>
-      </c>
+          <t>Maximo Encarnacion</t>
+        </is>
+      </c>
+      <c r="H346" s="12" t="inlineStr"/>
       <c r="I346" s="10" t="n">
         <v>3</v>
       </c>
       <c r="J346" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347" ht="18" customHeight="1">
@@ -13900,18 +14878,18 @@
       </c>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C347" s="7" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D347" s="16" t="n">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>mesa_5</t>
+          <t>mesa_6</t>
         </is>
       </c>
       <c r="F347" s="10" t="inlineStr">
@@ -13921,34 +14899,37 @@
       </c>
       <c r="G347" s="11" t="inlineStr">
         <is>
-          <t>Maximo Encarnacion</t>
+          <t>Wagner Trujillo</t>
         </is>
       </c>
       <c r="H347" s="12" t="inlineStr"/>
       <c r="I347" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="J347" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="348" ht="18" customHeight="1">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C348" s="7" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D348" s="16" t="n">
         <v>46179</v>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>mesa_5</t>
+          <t>mesa_1</t>
         </is>
       </c>
       <c r="F348" s="10" t="inlineStr">
@@ -13958,37 +14939,37 @@
       </c>
       <c r="G348" s="11" t="inlineStr">
         <is>
-          <t>Maximo Encarnacion</t>
+          <t>Wilder Trujillo</t>
         </is>
       </c>
       <c r="H348" s="12" t="inlineStr"/>
       <c r="I348" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J348" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349" ht="18" customHeight="1">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C349" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D349" s="16" t="n">
         <v>46178</v>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>mesa_6</t>
+          <t>mesa_2</t>
         </is>
       </c>
       <c r="F349" s="10" t="inlineStr">
@@ -13998,15 +14979,15 @@
       </c>
       <c r="G349" s="11" t="inlineStr">
         <is>
-          <t>Wagner Trujillo</t>
+          <t>Yerald Romero</t>
         </is>
       </c>
       <c r="H349" s="12" t="inlineStr"/>
       <c r="I349" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J349" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
